--- a/results/tables/Table 1.xlsx
+++ b/results/tables/Table 1.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tao25\Documents\Liposarcoma\2\results\tables\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92C98DBF-807C-4A1A-A80C-8BA0A023C1B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="21000" windowHeight="8955"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="61">
   <si>
     <r>
       <t>Table 1</t>
@@ -75,7 +81,7 @@
     <t>Biological samples</t>
   </si>
   <si>
-    <t>TCGA DDLPS RNA_x001e_seq data (n=50)</t>
+    <t>TCGA DDLPS RNA_x001E_seq data (n=50)</t>
   </si>
   <si>
     <t>The Cancer Genome Atlas (TCGA)</t>
@@ -102,7 +108,7 @@
     <t>TCGA clinical data</t>
   </si>
   <si>
-    <t>TCGA_x001e_SARC; https://portal.gdc.cancer.gov/</t>
+    <t>TCGA_x001E_SARC; https://portal.gdc.cancer.gov/</t>
   </si>
   <si>
     <t>Critical commercial assays</t>
@@ -114,7 +120,7 @@
     <t>Deposited data</t>
   </si>
   <si>
-    <t>Differentially expressed genes (high_x001e_score vs low_x001e_score)</t>
+    <t>Differentially expressed genes (high_x001E_score vs low_x001E_score)</t>
   </si>
   <si>
     <t>This study</t>
@@ -344,7 +350,7 @@
     <t>R Core Team</t>
   </si>
   <si>
-    <t>RRID:SCR_001905; https://www.r_x001e_project.org/</t>
+    <t>RRID:SCR_001905; https://www.r_x001E_project.org/</t>
   </si>
   <si>
     <t>limma v3.56.2</t>
@@ -362,25 +368,25 @@
     <t>https://bioconductor.org/packages/clusterProfiler/</t>
   </si>
   <si>
-    <t>survival v3.5_x001e_5</t>
+    <t>survival v3.5_x001E_5</t>
   </si>
   <si>
     <t>CRAN</t>
   </si>
   <si>
-    <t>https://cran.r_x001e_project.org/package=survival</t>
+    <t>https://cran.r_x001E_project.org/package=survival</t>
   </si>
   <si>
     <t>survminer v0.4.9</t>
   </si>
   <si>
-    <t>https://cran.r_x001e_project.org/package=survminer</t>
+    <t>https://cran.r_x001E_project.org/package=survminer</t>
   </si>
   <si>
     <t>timeROC</t>
   </si>
   <si>
-    <t>https://cran.r_x001e_project.org/package=timeROC</t>
+    <t>https://cran.r_x001E_project.org/package=timeROC</t>
   </si>
   <si>
     <t>DoRothEA</t>
@@ -392,7 +398,7 @@
     <t>ggplot2 v3.5.0</t>
   </si>
   <si>
-    <t>https://cran.r_x001e_project.org/package=ggplot2</t>
+    <t>https://cran.r_x001E_project.org/package=ggplot2</t>
   </si>
   <si>
     <t>ggtree v4.2.0</t>
@@ -416,30 +422,10 @@
     <t>https://www.gsea-msigdb.org/gsea/msigdb/</t>
   </si>
   <si>
-    <r>
-      <t>https://bioconductor.org/packages/ComplexHeatmap</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF333333"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>/</t>
-    </r>
-  </si>
-  <si>
-    <t>https://bioconductor.org/packages/GSVA/</t>
-  </si>
-  <si>
-    <t>https://cran.r_x001e_project.org/package=pheatmap</t>
-  </si>
-  <si>
     <t>Other</t>
   </si>
   <si>
-    <t>TCGA_x001e_SARC</t>
+    <t>TCGA_x001E_SARC</t>
   </si>
   <si>
     <t>Available from corresponding author upon reasonable request</t>
@@ -451,18 +437,12 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="25">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -493,150 +473,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <i/>
       <sz val="12"/>
       <color rgb="FF333333"/>
@@ -644,7 +480,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -669,194 +505,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="11">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -884,256 +534,14 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="35" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+  <cellXfs count="11">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1141,9 +549,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="top" wrapText="1"/>
@@ -1157,65 +562,30 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1465,25 +835,25 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:C37"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:C32"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="2" width="30.4690265486726" customWidth="1"/>
-    <col min="3" max="3" width="60.3362831858407" customWidth="1"/>
+    <col min="1" max="2" width="30.46484375" customWidth="1"/>
+    <col min="3" max="3" width="60.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="62.25" spans="1:3">
+    <row r="1" spans="1:3" ht="15.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" ht="61.5" spans="1:3">
+    <row r="2" spans="1:3" ht="15">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -1494,371 +864,333 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1" spans="1:3">
-      <c r="A3" s="3" t="s">
+    <row r="3" spans="1:3" ht="15" customHeight="1">
+      <c r="A3" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-    </row>
-    <row r="4" ht="46.15" spans="1:3">
-      <c r="A4" s="4" t="s">
+      <c r="B3" s="7"/>
+      <c r="C3" s="7"/>
+    </row>
+    <row r="4" spans="1:3" ht="15.4">
+      <c r="A4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="1:3">
-      <c r="A5" s="3" t="s">
+    <row r="5" spans="1:3" ht="15" customHeight="1">
+      <c r="A5" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-    </row>
-    <row r="6" ht="76.9" spans="1:3">
-      <c r="A6" s="4" t="s">
+      <c r="B5" s="7"/>
+      <c r="C5" s="7"/>
+    </row>
+    <row r="6" spans="1:3" ht="30.75">
+      <c r="A6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="7" ht="138.4" spans="1:3">
-      <c r="A7" s="5" t="s">
+    <row r="7" spans="1:3" ht="30.75">
+      <c r="A7" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="8" ht="153.75" spans="1:3">
-      <c r="A8" s="4" t="s">
+    <row r="8" spans="1:3" ht="30.75">
+      <c r="A8" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="9" ht="92.25" spans="1:3">
-      <c r="A9" s="5" t="s">
+    <row r="9" spans="1:3" ht="30.75">
+      <c r="A9" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:3">
-      <c r="A10" s="3" t="s">
+    <row r="10" spans="1:3" ht="15" customHeight="1">
+      <c r="A10" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-    </row>
-    <row r="11" ht="123" spans="1:3">
-      <c r="A11" s="5" t="s">
+      <c r="B10" s="7"/>
+      <c r="C10" s="7"/>
+    </row>
+    <row r="11" spans="1:3" ht="46.15">
+      <c r="A11" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" spans="1:3">
-      <c r="A12" s="3" t="s">
+    <row r="12" spans="1:3" ht="15" customHeight="1">
+      <c r="A12" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-    </row>
-    <row r="13" ht="107.65" spans="1:3">
-      <c r="A13" s="5" t="s">
+      <c r="B12" s="7"/>
+      <c r="C12" s="7"/>
+    </row>
+    <row r="13" spans="1:3" ht="30.75">
+      <c r="A13" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="5" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="14" ht="138.4" spans="1:3">
-      <c r="A14" s="4" t="s">
+    <row r="14" spans="1:3" ht="15.4">
+      <c r="A14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="6" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="15" ht="76.9" spans="1:3">
-      <c r="A15" s="5" t="s">
+    <row r="15" spans="1:3" ht="30.75">
+      <c r="A15" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="5" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="16" ht="153.75" spans="1:3">
-      <c r="A16" s="4" t="s">
+    <row r="16" spans="1:3" ht="30.75">
+      <c r="A16" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C16" s="6" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1" spans="1:3">
-      <c r="A17" s="3" t="s">
+    <row r="17" spans="1:3" ht="15" customHeight="1">
+      <c r="A17" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-    </row>
-    <row r="18" ht="107.65" spans="1:3">
-      <c r="A18" s="4" t="s">
+      <c r="B17" s="7"/>
+      <c r="C17" s="7"/>
+    </row>
+    <row r="18" spans="1:3" ht="15.4">
+      <c r="A18" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="3" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="19" ht="76.9" spans="1:3">
-      <c r="A19" s="5" t="s">
+    <row r="19" spans="1:3" ht="15.4">
+      <c r="A19" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="4" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="20" ht="92.25" spans="1:3">
-      <c r="A20" s="4" t="s">
+    <row r="20" spans="1:3" ht="15.4">
+      <c r="A20" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="3" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="21" ht="92.25" spans="1:3">
-      <c r="A21" s="5" t="s">
+    <row r="21" spans="1:3" ht="15.4">
+      <c r="A21" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="4" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="22" ht="92.25" spans="1:3">
-      <c r="A22" s="4" t="s">
+    <row r="22" spans="1:3" ht="15.4">
+      <c r="A22" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C22" s="3" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="23" ht="92.25" spans="1:3">
-      <c r="A23" s="5" t="s">
+    <row r="23" spans="1:3" ht="15.4">
+      <c r="A23" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="C23" s="4" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="24" ht="92.25" spans="1:3">
-      <c r="A24" s="4" t="s">
+    <row r="24" spans="1:3" ht="15.4">
+      <c r="A24" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B24" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="C24" s="3" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="25" ht="92.25" spans="1:3">
-      <c r="A25" s="5" t="s">
+    <row r="25" spans="1:3" ht="15.4">
+      <c r="A25" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B25" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="C25" s="5" t="s">
+      <c r="C25" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="26" ht="76.9" spans="1:3">
-      <c r="A26" s="4" t="s">
+    <row r="26" spans="1:3" ht="15.4">
+      <c r="A26" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="B26" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C26" s="4" t="s">
+      <c r="C26" s="3" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="27" ht="76.9" spans="1:3">
-      <c r="A27" s="5" t="s">
+    <row r="27" spans="1:3" ht="15.4">
+      <c r="A27" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B27" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C27" s="5" t="s">
+      <c r="C27" s="4" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="28" ht="76.9" spans="1:3">
-      <c r="A28" s="4" t="s">
+    <row r="28" spans="1:3" ht="15.4">
+      <c r="A28" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B28" s="4" t="s">
+      <c r="B28" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C28" s="4" t="s">
+      <c r="C28" s="3" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1" spans="1:3">
-      <c r="A29" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B29" s="3"/>
-      <c r="C29" s="3"/>
-    </row>
-    <row r="30" ht="30.75" customHeight="1" spans="1:3">
-      <c r="A30" s="4" t="s">
+    <row r="29" spans="1:3" ht="15" customHeight="1">
+      <c r="A29" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B30" s="4"/>
-      <c r="C30" s="4"/>
-    </row>
-    <row r="31" ht="30.75" customHeight="1" spans="1:3">
-      <c r="A31" s="5" t="s">
+      <c r="B29" s="7"/>
+      <c r="C29" s="7"/>
+    </row>
+    <row r="30" spans="1:3" ht="15.4" customHeight="1">
+      <c r="A30" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="B31" s="5"/>
-      <c r="C31" s="5"/>
-    </row>
-    <row r="32" ht="30.75" customHeight="1" spans="1:3">
-      <c r="A32" s="4" t="s">
+      <c r="B30" s="8"/>
+      <c r="C30" s="8"/>
+    </row>
+    <row r="31" spans="1:3" ht="15.4" customHeight="1">
+      <c r="A31" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B32" s="4"/>
-      <c r="C32" s="4"/>
-    </row>
-    <row r="33" ht="15" customHeight="1" spans="1:3">
-      <c r="A33" s="3" t="s">
+      <c r="B31" s="9"/>
+      <c r="C31" s="9"/>
+    </row>
+    <row r="32" spans="1:3" ht="15.4" customHeight="1">
+      <c r="A32" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="B33" s="3"/>
-      <c r="C33" s="3"/>
-    </row>
-    <row r="34" ht="15.4" customHeight="1" spans="1:3">
-      <c r="A34" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="B34" s="4"/>
-      <c r="C34" s="4"/>
-    </row>
-    <row r="35" ht="30.75" customHeight="1" spans="1:3">
-      <c r="A35" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="B35" s="5"/>
-      <c r="C35" s="5"/>
-    </row>
-    <row r="36" ht="46.9" customHeight="1" spans="1:3">
-      <c r="A36" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="B36" s="8"/>
-      <c r="C36" s="8"/>
-    </row>
-    <row r="37" ht="14.25"/>
+      <c r="B32" s="10"/>
+      <c r="C32" s="10"/>
+    </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="9">
+    <mergeCell ref="A30:C30"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="A29:C29"/>
     <mergeCell ref="A3:C3"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="A10:C10"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="A17:C17"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="A30:C30"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="A34:C34"/>
-    <mergeCell ref="A35:C35"/>
-    <mergeCell ref="A36:C36"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>